--- a/data/trans_camb/P05B_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P05B_R-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-1,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,24</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,83</t>
+          <t>-3,21; -0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,83</t>
+          <t>-2,26; 0,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,89</t>
+          <t>-3,15; -0,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -1,29</t>
+          <t>-3,98; -1,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; -1,25</t>
+          <t>-3,9; -1,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; -1,5</t>
+          <t>-4,15; -1,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; -1,35</t>
+          <t>-3,13; -1,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,65; -0,69</t>
+          <t>-2,61; -0,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -1,47</t>
+          <t>-3,12; -1,52</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-89,17%</t>
+          <t>-89,65%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-90,44%</t>
+          <t>-90,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-89,83%</t>
+          <t>-90,11%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,46</t>
+          <t>-100,0; -48,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 64,15</t>
+          <t>-77,3; 58,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -56,26</t>
+          <t>-100,0; -50,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-96,41; -51,05</t>
+          <t>-96,78; -51,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-96,02; -48,93</t>
+          <t>-96,76; -46,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-97,61; -75,82</t>
+          <t>-96,85; -74,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,33; -67,38</t>
+          <t>-95,34; -67,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,97; -27,61</t>
+          <t>-81,45; -26,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-96,12; -76,86</t>
+          <t>-96,1; -77,5</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-1,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-3,79</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,86</t>
+          <t>-2,85</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,54</t>
+          <t>-2,08; 0,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,01</t>
+          <t>-2,31; -0,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; -1,02</t>
+          <t>-3,12; -0,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,71; -0,2</t>
+          <t>-3,51; -0,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,36; -1,14</t>
+          <t>-4,26; -1,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -2,46</t>
+          <t>-5,38; -2,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; -0,28</t>
+          <t>-2,37; -0,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; -1,02</t>
+          <t>-3,02; -0,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -2,04</t>
+          <t>-3,85; -2,02</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-83,17%</t>
+          <t>-81,37%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-84,59%</t>
+          <t>-85,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-84,57%</t>
+          <t>-84,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 33,77</t>
+          <t>-66,76; 39,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 3,63</t>
+          <t>-76,63; 1,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-96,28; -50,73</t>
+          <t>-94,28; -42,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 1,24</t>
+          <t>-64,41; -2,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-78,96; -28,65</t>
+          <t>-79,74; -36,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-93,1; -65,72</t>
+          <t>-93,51; -70,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,97; -9,79</t>
+          <t>-59,0; -8,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -35,07</t>
+          <t>-74,35; -31,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-92,63; -72,16</t>
+          <t>-91,18; -70,7</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,61</t>
+          <t>-3,49</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-2,75</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,21</t>
+          <t>-2,05; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,67</t>
+          <t>-2,36; 0,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; -0,62</t>
+          <t>-3,39; -0,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; -1,32</t>
+          <t>-4,63; -1,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,48</t>
+          <t>-2,74; 1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; -2,33</t>
+          <t>-5,19; -2,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; -0,42</t>
+          <t>-2,88; -0,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,69</t>
+          <t>-1,91; 0,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; -1,82</t>
+          <t>-3,85; -1,73</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-76,37%</t>
+          <t>-74,91%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-92,31%</t>
+          <t>-89,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-86,85%</t>
+          <t>-83,8%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 87,82</t>
+          <t>-61,43; 87,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-74,1; 49,42</t>
+          <t>-71,39; 70,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-96,38; -14,94</t>
+          <t>-93,93; -17,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-89,4; -37,98</t>
+          <t>-87,53; -39,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-51,64; 48,3</t>
+          <t>-52,52; 46,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-98,26; -79,12</t>
+          <t>-96,08; -72,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,34; -15,86</t>
+          <t>-71,52; -12,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,24; 29,91</t>
+          <t>-49,36; 24,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-95,0; -70,03</t>
+          <t>-92,34; -65,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-1,88</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,48</t>
+          <t>-3,42</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-2,69</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,79; -0,48</t>
+          <t>-3,89; -0,49</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; -1,75</t>
+          <t>-4,98; -1,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,1</t>
+          <t>-3,66; -0,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,4; -2,94</t>
+          <t>-6,68; -2,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -1,77</t>
+          <t>-5,9; -2,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,39; -1,81</t>
+          <t>-5,25; -1,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,89; -2,38</t>
+          <t>-4,76; -2,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -2,27</t>
+          <t>-4,82; -2,43</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -1,38</t>
+          <t>-3,97; -1,43</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-36,68%</t>
+          <t>-40,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-52,63%</t>
+          <t>-51,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,4%</t>
+          <t>-47,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-69,63; -11,49</t>
+          <t>-69,68; -6,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,28; -43,24</t>
+          <t>-85,66; -42,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 4,35</t>
+          <t>-63,4; 0,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-82,1; -50,73</t>
+          <t>-83,64; -51,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,06; -30,52</t>
+          <t>-74,8; -36,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,91; -32,45</t>
+          <t>-67,69; -31,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,07; -46,44</t>
+          <t>-73,32; -46,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-73,77; -45,81</t>
+          <t>-75,75; -49,1</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,55; -27,5</t>
+          <t>-61,97; -28,95</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,46</t>
+          <t>-3,41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,68</t>
+          <t>-2,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,03; -0,53</t>
+          <t>-2,04; -0,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,3; -0,8</t>
+          <t>-2,32; -0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,55; -1,13</t>
+          <t>-2,57; -1,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; -2,26</t>
+          <t>-3,92; -2,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -1,68</t>
+          <t>-3,54; -1,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; -2,68</t>
+          <t>-4,22; -2,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,71; -1,59</t>
+          <t>-2,76; -1,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,68; -1,53</t>
+          <t>-2,71; -1,53</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -2,12</t>
+          <t>-3,17; -2,13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-63,46%</t>
+          <t>-63,51%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-73,84%</t>
+          <t>-72,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-69,87%</t>
+          <t>-69,22%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-60,6; -20,57</t>
+          <t>-60,55; -22,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,37; -31,68</t>
+          <t>-68,54; -33,87</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -43,0</t>
+          <t>-75,21; -45,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-75,45; -53,51</t>
+          <t>-74,84; -51,95</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-65,78; -39,58</t>
+          <t>-66,53; -40,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,54; -64,06</t>
+          <t>-80,34; -63,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-65,27; -46,11</t>
+          <t>-65,84; -46,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-63,75; -43,66</t>
+          <t>-64,08; -43,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-76,91; -61,6</t>
+          <t>-76,13; -61,83</t>
         </is>
       </c>
     </row>
